--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_gmprob/sub-0006_ses-01_GMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_gmprob/sub-0006_ses-01_GMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
